--- a/dataset/construct/dataset_splits/data_size/10_percent/lmu/fold3.xlsx
+++ b/dataset/construct/dataset_splits/data_size/10_percent/lmu/fold3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN15"/>
+  <dimension ref="A1:AK15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>52251082</v>
+        <v>53557932</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,117 +625,114 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>78.0506502395619</v>
+        <v>84.5119780971937</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>23.8884409806205</v>
       </c>
       <c r="E2" t="n">
-        <v>25.8805706350208</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>65</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>699</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1278</v>
+      </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>365</v>
       </c>
       <c r="K2" t="n">
-        <v>306</v>
+        <v>2342</v>
       </c>
       <c r="L2" t="n">
-        <v>117</v>
+        <v>692</v>
       </c>
       <c r="M2" t="n">
-        <v>250</v>
+        <v>1188</v>
       </c>
       <c r="N2" t="n">
-        <v>673</v>
+        <v>365</v>
       </c>
       <c r="O2" t="n">
-        <v>306</v>
+        <v>2245</v>
       </c>
       <c r="P2" t="n">
-        <v>117</v>
+        <v>76</v>
       </c>
       <c r="Q2" t="n">
-        <v>250</v>
+        <v>32</v>
       </c>
       <c r="R2" t="n">
-        <v>673</v>
+        <v>176</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>284</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>31.9</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>33.32704508344288</v>
       </c>
       <c r="X2" t="n">
-        <v>25.4</v>
+        <v>31.91538243211462</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>84.90000000000001</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>525.9</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
+        <v>158</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>52849965</v>
+        <v>52530187</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -758,69 +740,79 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>72.18069815195069</v>
+        <v>78.5516769336071</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>27.9296875</v>
       </c>
       <c r="E3" t="n">
-        <v>27.7777777777778</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>55</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>96</v>
+      </c>
+      <c r="I3" t="n">
+        <v>79</v>
+      </c>
       <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+        <v>258</v>
+      </c>
+      <c r="K3" t="n">
+        <v>433</v>
+      </c>
+      <c r="L3" t="n">
+        <v>72</v>
+      </c>
+      <c r="M3" t="n">
+        <v>41</v>
+      </c>
+      <c r="N3" t="n">
+        <v>58</v>
+      </c>
       <c r="O3" t="n">
-        <v>158.73917</v>
+        <v>171</v>
       </c>
       <c r="P3" t="n">
-        <v>367.80267</v>
+        <v>136</v>
       </c>
       <c r="Q3" t="n">
-        <v>85.01295</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>611.5549</v>
+        <v>19</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>24.5</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>24.89183309957243</v>
       </c>
       <c r="X3" t="n">
-        <v>27.81884</v>
+        <v>23.74159106829735</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>89.7937</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>601.7905</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -847,24 +839,15 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>134</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>97</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>54535871</v>
+        <v>52059579</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -872,74 +855,86 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>75.41409993155369</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>85.6125941136208</v>
+      </c>
+      <c r="D4" t="n">
+        <v>25.6543723973825</v>
+      </c>
       <c r="E4" t="n">
-        <v>32.8719723183391</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>53</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>320</v>
+      </c>
+      <c r="I4" t="n">
+        <v>653</v>
+      </c>
       <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+        <v>290</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1263</v>
+      </c>
+      <c r="L4" t="n">
+        <v>313</v>
+      </c>
+      <c r="M4" t="n">
+        <v>268</v>
+      </c>
+      <c r="N4" t="n">
+        <v>202</v>
+      </c>
       <c r="O4" t="n">
-        <v>234</v>
+        <v>783</v>
       </c>
       <c r="P4" t="n">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="Q4" t="n">
-        <v>282</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>647</v>
+        <v>69</v>
       </c>
       <c r="S4" t="n">
-        <v>16</v>
+        <v>182</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>27.4</v>
       </c>
       <c r="V4" t="n">
-        <v>16</v>
+        <v>0.28</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>28.48873481344927</v>
       </c>
       <c r="X4" t="n">
-        <v>25.1</v>
+        <v>27.45001206874542</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>81.2</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>494.5</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
@@ -957,24 +952,15 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>211</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>178</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>51223067</v>
+        <v>54585763</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -982,82 +968,80 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>82.6255989048597</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>71.4633812457221</v>
+      </c>
+      <c r="D5" t="n">
+        <v>24.8356464572681</v>
+      </c>
       <c r="E5" t="n">
-        <v>28.6501377410468</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>45</v>
+      </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" t="n">
-        <v>55</v>
-      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>287</v>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>588</v>
+        <v>343</v>
       </c>
       <c r="M5" t="n">
-        <v>254</v>
+        <v>739</v>
       </c>
       <c r="N5" t="n">
-        <v>1129</v>
+        <v>892</v>
       </c>
       <c r="O5" t="n">
-        <v>273</v>
+        <v>1974</v>
       </c>
       <c r="P5" t="n">
-        <v>573</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>146</v>
+        <v>24.1</v>
       </c>
       <c r="V5" t="n">
-        <v>229</v>
+        <v>0.16</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>24.70084716786215</v>
       </c>
       <c r="X5" t="n">
-        <v>29.1</v>
+        <v>24.32959235884105</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>92</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>629.5</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1066,29 +1050,24 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
+        <v>112</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>54197905</v>
+        <v>51368301</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1096,77 +1075,91 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>89.9411362080767</v>
-      </c>
-      <c r="D6" t="inlineStr"/>
+        <v>77.4893908281999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>18.4672206832872</v>
+      </c>
       <c r="E6" t="n">
-        <v>25.6055363321799</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>23</v>
+      </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>74</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>394</v>
+      </c>
+      <c r="I6" t="n">
+        <v>261</v>
+      </c>
       <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+        <v>398</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1053</v>
+      </c>
+      <c r="L6" t="n">
+        <v>360</v>
+      </c>
+      <c r="M6" t="n">
+        <v>252</v>
+      </c>
+      <c r="N6" t="n">
+        <v>351</v>
+      </c>
       <c r="O6" t="n">
-        <v>843</v>
+        <v>963</v>
       </c>
       <c r="P6" t="n">
-        <v>471</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>651</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1964</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>136</v>
+        <v>29.4</v>
       </c>
       <c r="V6" t="n">
-        <v>366</v>
+        <v>0.23</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>29.41183348338226</v>
       </c>
       <c r="X6" t="n">
-        <v>24.1</v>
+        <v>28.9050132201183</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>76.7</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>448.4</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1180,21 +1173,12 @@
       <c r="AI6" t="n">
         <v>0</v>
       </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>54836611</v>
+        <v>52803803</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1202,65 +1186,79 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>90.24503764544831</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
+        <v>87.45516769336071</v>
+      </c>
+      <c r="D7" t="n">
+        <v>19.2335607490202</v>
+      </c>
       <c r="E7" t="n">
-        <v>30.8248299319728</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>60</v>
+      </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>55</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
+        <v>134</v>
+      </c>
+      <c r="I7" t="n">
+        <v>311</v>
+      </c>
       <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+        <v>315</v>
+      </c>
+      <c r="K7" t="n">
+        <v>760</v>
+      </c>
+      <c r="L7" t="n">
+        <v>134</v>
+      </c>
+      <c r="M7" t="n">
+        <v>311</v>
+      </c>
+      <c r="N7" t="n">
+        <v>315</v>
+      </c>
       <c r="O7" t="n">
-        <v>75</v>
+        <v>760</v>
       </c>
       <c r="P7" t="n">
-        <v>157</v>
+        <v>127</v>
       </c>
       <c r="Q7" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>349</v>
+        <v>287</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>414</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>100</v>
+        <v>20.3</v>
       </c>
       <c r="V7" t="n">
-        <v>100</v>
+        <v>0.22</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>20.02169184096043</v>
       </c>
       <c r="X7" t="n">
-        <v>24.8</v>
+        <v>19.69013563619756</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>471.8</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1278,29 +1276,20 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>54291618</v>
+        <v>55648067</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1308,76 +1297,80 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>79.0198494182067</v>
+        <v>79.90143737166321</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>26.3100595151691</v>
       </c>
       <c r="E8" t="n">
-        <v>25.1428571428571</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>55</v>
+      </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="n">
-        <v>55</v>
-      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>78.24156000000001</v>
+      </c>
+      <c r="M8" t="n">
+        <v>46.56002</v>
+      </c>
+      <c r="N8" t="n">
+        <v>81.27647399999999</v>
+      </c>
       <c r="O8" t="n">
-        <v>395</v>
+        <v>206.078054</v>
       </c>
       <c r="P8" t="n">
-        <v>473</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>343</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1211</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>21.610773</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>22.29482231567043</v>
       </c>
       <c r="X8" t="n">
-        <v>25.1</v>
+        <v>21.63136061077274</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>82.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>491.9</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1386,33 +1379,24 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="AK8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>214</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>54368304</v>
+        <v>54388499</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1420,109 +1404,106 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>76.766598220397</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
+        <v>76.99383983572891</v>
+      </c>
+      <c r="D9" t="n">
+        <v>23.8894628099174</v>
+      </c>
       <c r="E9" t="n">
-        <v>27.1808999081726</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>39</v>
+      </c>
       <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>61</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>1327</v>
+      </c>
+      <c r="M9" t="n">
+        <v>921</v>
+      </c>
+      <c r="N9" t="n">
+        <v>585</v>
+      </c>
       <c r="O9" t="n">
-        <v>218</v>
+        <v>2833</v>
       </c>
       <c r="P9" t="n">
-        <v>474</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>984</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>29.5</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>30.84422797120932</v>
       </c>
       <c r="X9" t="n">
-        <v>24.2</v>
+        <v>30.02633713303987</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.17</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="n">
-        <v>77.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>467.5</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="AK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>122</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>146</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>52823268</v>
+        <v>54747624</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1530,77 +1511,71 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>74.16290212183441</v>
+        <v>74.3572895277207</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>24.441802087462</v>
       </c>
       <c r="E10" t="n">
-        <v>23.8085327783559</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
-      <c r="H10" t="n">
-        <v>55</v>
-      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>121</v>
-      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>53</v>
+        <v>825</v>
       </c>
       <c r="M10" t="n">
-        <v>157</v>
+        <v>295</v>
       </c>
       <c r="N10" t="n">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="O10" t="n">
-        <v>107</v>
+        <v>1456</v>
       </c>
       <c r="P10" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>299</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>255</v>
+        <v>26.2</v>
       </c>
       <c r="V10" t="n">
-        <v>433</v>
+        <v>0.25</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>26.35605857601787</v>
       </c>
       <c r="X10" t="n">
-        <v>24.7</v>
+        <v>25.87656616663467</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>79.2</v>
+        <v>1</v>
       </c>
       <c r="AA10" t="n">
-        <v>479.6</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1618,29 +1593,24 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
+        <v>102</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>54904200</v>
+        <v>54054177</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1648,65 +1618,71 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>80.87337440109511</v>
-      </c>
-      <c r="D11" t="inlineStr"/>
+        <v>87.0718685831622</v>
+      </c>
+      <c r="D11" t="n">
+        <v>20.829995193078</v>
+      </c>
       <c r="E11" t="n">
-        <v>25.1807851239669</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>59</v>
+      </c>
       <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>45</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>242</v>
+      </c>
+      <c r="M11" t="n">
+        <v>246</v>
+      </c>
+      <c r="N11" t="n">
+        <v>250</v>
+      </c>
       <c r="O11" t="n">
-        <v>451</v>
+        <v>738</v>
       </c>
       <c r="P11" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>732</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>21.6</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>21.70873423773453</v>
       </c>
       <c r="X11" t="n">
-        <v>25.7</v>
+        <v>21.33502137901016</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>82.59999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA11" t="n">
-        <v>512.9</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1724,33 +1700,24 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="AK11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>204</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>154</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>52646009</v>
+        <v>54913375</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1758,117 +1725,106 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>85.7029431895962</v>
+        <v>75.1786447638604</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>29.320987654321</v>
       </c>
       <c r="E12" t="n">
-        <v>22.5827091723437</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="n">
-        <v>60</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>654</v>
-      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>155</v>
+        <v>216</v>
       </c>
       <c r="M12" t="n">
-        <v>255</v>
+        <v>293</v>
       </c>
       <c r="N12" t="n">
-        <v>1064</v>
+        <v>284</v>
       </c>
       <c r="O12" t="n">
-        <v>654</v>
+        <v>793</v>
       </c>
       <c r="P12" t="n">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="Q12" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>919</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>61</v>
+        <v>26.9</v>
       </c>
       <c r="V12" t="n">
-        <v>157</v>
+        <v>0.18</v>
       </c>
       <c r="W12" t="n">
-        <v>2</v>
+        <v>26.6107064849649</v>
       </c>
       <c r="X12" t="n">
-        <v>28.4</v>
+        <v>26.12142936409824</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>90.5</v>
+        <v>1</v>
       </c>
       <c r="AA12" t="n">
-        <v>611.7</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="AK12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="inlineStr"/>
+        <v>106</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>53613169</v>
+        <v>55818337</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1876,79 +1832,77 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>74.92402464065709</v>
-      </c>
-      <c r="D13" t="inlineStr"/>
+        <v>83.7070499657769</v>
+      </c>
+      <c r="D13" t="n">
+        <v>28.3675236644868</v>
+      </c>
       <c r="E13" t="n">
-        <v>25.0995015956112</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>42</v>
+      </c>
       <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>60</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>304</v>
-      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>457</v>
+        <v>127.83168</v>
       </c>
       <c r="M13" t="n">
-        <v>267</v>
+        <v>267.0387</v>
       </c>
       <c r="N13" t="n">
-        <v>1029</v>
+        <v>151.37073</v>
       </c>
       <c r="O13" t="n">
-        <v>296</v>
+        <v>546.24111</v>
       </c>
       <c r="P13" t="n">
-        <v>409</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>243</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>947</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>25.884556</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="W13" t="n">
-        <v>2</v>
+        <v>26.31333947943269</v>
       </c>
       <c r="X13" t="n">
-        <v>24.7</v>
+        <v>25.8501732722776</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>79.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>471.8</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -1957,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -1966,27 +1920,18 @@
         <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>174</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>53346157</v>
+        <v>53762035</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1994,73 +1939,79 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>71.668720054757</v>
-      </c>
-      <c r="D14" t="inlineStr"/>
+        <v>83.25256673511289</v>
+      </c>
+      <c r="D14" t="n">
+        <v>27.1808999081726</v>
+      </c>
       <c r="E14" t="n">
-        <v>30.4705215419501</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>50</v>
+      </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>55</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
+        <v>183</v>
+      </c>
+      <c r="I14" t="n">
+        <v>383</v>
+      </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="K14" t="n">
-        <v>169</v>
+        <v>831</v>
       </c>
       <c r="L14" t="n">
-        <v>254</v>
+        <v>171</v>
       </c>
       <c r="M14" t="n">
-        <v>210</v>
+        <v>54</v>
       </c>
       <c r="N14" t="n">
-        <v>632</v>
+        <v>155</v>
       </c>
       <c r="O14" t="n">
-        <v>169</v>
+        <v>380</v>
       </c>
       <c r="P14" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>485</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>20.6</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="W14" t="n">
-        <v>1</v>
+        <v>22.56817093043076</v>
       </c>
       <c r="X14" t="n">
-        <v>27.3</v>
+        <v>21.33203725124131</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>87</v>
+        <v>1</v>
       </c>
       <c r="AA14" t="n">
-        <v>566.9</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2078,33 +2029,24 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="AK14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>173</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>54108010</v>
+        <v>54623649</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2112,76 +2054,80 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>87.4715947980835</v>
+        <v>87.49897330595481</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>29.0174471992654</v>
       </c>
       <c r="E15" t="n">
-        <v>23.4375</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>40</v>
+      </c>
       <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>66</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>763</v>
+      </c>
+      <c r="M15" t="n">
+        <v>412</v>
+      </c>
+      <c r="N15" t="n">
+        <v>464</v>
+      </c>
       <c r="O15" t="n">
-        <v>120</v>
+        <v>1639</v>
       </c>
       <c r="P15" t="n">
-        <v>243</v>
+        <v>94</v>
       </c>
       <c r="Q15" t="n">
-        <v>197</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>560</v>
+        <v>69</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>114</v>
+        <v>22.9</v>
       </c>
       <c r="V15" t="n">
-        <v>114</v>
+        <v>0.27</v>
       </c>
       <c r="W15" t="n">
-        <v>1</v>
+        <v>23.2684526800351</v>
       </c>
       <c r="X15" t="n">
-        <v>25.4</v>
+        <v>22.29512767993508</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>81.40000000000001</v>
+        <v>1</v>
       </c>
       <c r="AA15" t="n">
-        <v>474.2</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2190,28 +2136,19 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="AK15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>126</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
